--- a/doanmon/FILE_3_TAO_MOI_VA_CAP_NHAT.xlsx
+++ b/doanmon/FILE_3_TAO_MOI_VA_CAP_NHAT.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>productCode</t>
   </si>
@@ -32,103 +32,106 @@
     <t>description</t>
   </si>
   <si>
-    <t>CAKE-CHOCO-001</t>
-  </si>
-  <si>
-    <t>Chocolate Fudge Cake Updated</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
+    <t>CAKE-BDAY-001</t>
+  </si>
+  <si>
+    <t>Rainbow Birthday Cake Updated</t>
+  </si>
+  <si>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>Updated price and restocking</t>
   </si>
   <si>
-    <t>CAKE-NEW-TIRAMISU-001</t>
-  </si>
-  <si>
-    <t>Tiramisu Classic</t>
-  </si>
-  <si>
-    <t>Italian coffee-flavored dessert</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-TIRAMISU-002</t>
-  </si>
-  <si>
-    <t>Tiramisu Deluxe</t>
-  </si>
-  <si>
-    <t>Premium tiramisu with mascarpone</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-CHEESE-001</t>
-  </si>
-  <si>
-    <t>New York Cheesecake</t>
-  </si>
-  <si>
-    <t>Vanilla</t>
-  </si>
-  <si>
-    <t>Classic creamy cheesecake</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-CHEESE-002</t>
-  </si>
-  <si>
-    <t>Blueberry Cheesecake</t>
-  </si>
-  <si>
-    <t>Fruit</t>
-  </si>
-  <si>
-    <t>Cheesecake with blueberry topping</t>
-  </si>
-  <si>
-    <t>CAKE-VANILLA-001</t>
-  </si>
-  <si>
-    <t>Classic Vanilla Sponge</t>
-  </si>
-  <si>
-    <t>Price updated and restocking</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-MATCHA-001</t>
-  </si>
-  <si>
-    <t>Matcha Green Tea Cake</t>
-  </si>
-  <si>
-    <t>Japanese matcha flavor</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-LEMON-001</t>
-  </si>
-  <si>
-    <t>Lemon Drizzle Cake</t>
-  </si>
-  <si>
-    <t>Tangy lemon cake with glaze</t>
-  </si>
-  <si>
-    <t>CAKE-NEW-COCONUT-001</t>
-  </si>
-  <si>
-    <t>Coconut Paradise</t>
-  </si>
-  <si>
-    <t>Tropical coconut cake</t>
-  </si>
-  <si>
-    <t>CAKE-SPECIAL-001</t>
-  </si>
-  <si>
-    <t>Red Velvet Classic</t>
+    <t>CAKE-NEW-PRINCESS-001</t>
+  </si>
+  <si>
+    <t>Princess Castle Cake</t>
+  </si>
+  <si>
+    <t>Beautiful princess themed castle cake</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-SUPERHERO-001</t>
+  </si>
+  <si>
+    <t>Superhero Birthday Cake</t>
+  </si>
+  <si>
+    <t>Action-packed superhero themed cake</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-WEDDING-003</t>
+  </si>
+  <si>
+    <t>Floral Wedding Cake</t>
+  </si>
+  <si>
+    <t>Wedding Cakes</t>
+  </si>
+  <si>
+    <t>Elegant floral decorated wedding cake</t>
+  </si>
+  <si>
+    <t>CAKE-CHEESE-002</t>
+  </si>
+  <si>
+    <t>Blueberry Cheesecake Updated</t>
+  </si>
+  <si>
+    <t>Cheese Cakes</t>
+  </si>
+  <si>
+    <t>Updated cheesecake with blueberry topping</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-CHEESE-004</t>
+  </si>
+  <si>
+    <t>Mango Cheesecake</t>
+  </si>
+  <si>
+    <t>Tropical mango cheesecake</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-GATAUX-003</t>
+  </si>
+  <si>
+    <t>Strawberry Gataux</t>
+  </si>
+  <si>
+    <t>Gataux</t>
+  </si>
+  <si>
+    <t>Fresh strawberry gataux</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-GATAUX-004</t>
+  </si>
+  <si>
+    <t>Chocolate Mousse Gataux</t>
+  </si>
+  <si>
+    <t>Rich chocolate mousse gataux</t>
+  </si>
+  <si>
+    <t>CAKE-GATAUX-001</t>
+  </si>
+  <si>
+    <t>Black Forest Gataux Updated</t>
   </si>
   <si>
     <t>Price increase and small restock</t>
+  </si>
+  <si>
+    <t>CAKE-NEW-BDAY-004</t>
+  </si>
+  <si>
+    <t>Dinosaur Birthday Cake</t>
+  </si>
+  <si>
+    <t>Fun dinosaur themed birthday cake</t>
   </si>
 </sst>
 </file>
@@ -192,12 +195,12 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.0078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.92578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.02734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.3828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.46875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.75" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="8.44140625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="28.05078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="34.59765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -228,7 +231,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>30.99</v>
+        <v>38.99</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>8</v>
@@ -248,7 +251,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>34.99</v>
+        <v>55.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
@@ -268,7 +271,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>38.5</v>
+        <v>48.5</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>8</v>
@@ -288,13 +291,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>32.99</v>
+        <v>200.0</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>18</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>30.0</v>
+        <v>8.0</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -328,10 +331,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>19.99</v>
+        <v>34.99</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>15.0</v>
@@ -348,76 +351,76 @@
         <v>28</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>29.99</v>
+        <v>42.99</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>25.0</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>21.5</v>
+        <v>46.5</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>35.0</v>
+        <v>18.0</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>26.99</v>
+        <v>48.99</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>31.99</v>
+        <v>44.99</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
